--- a/frontend/public/batch-registration-template.xlsx
+++ b/frontend/public/batch-registration-template.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>瑞安市实验中学</t>
+          <t>安阳实验</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>安阳新纪元</t>
+          <t>新纪元</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>瑞祥实验学校</t>
+          <t>瑞祥实验</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>集云实验学校</t>
+          <t>集云学校</t>
         </is>
       </c>
     </row>

--- a/frontend/public/batch-registration-template.xlsx
+++ b/frontend/public/batch-registration-template.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>必填</t>
+          <t>必填，11位中国大陆手机号</t>
         </is>
       </c>
     </row>
